--- a/बजेट माग estimate/thekka/ओपी खोला रातोमाटे खानेपानी/ओपी खोला रातोमाटे खानेपानी - sir.xlsx
+++ b/बजेट माग estimate/thekka/ओपी खोला रातोमाटे खानेपानी/ओपी खोला रातोमाटे खानेपानी - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7AF28A-A7B9-48AD-ADFB-7F966871CD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C00E2E-BFA4-450D-94D3-9588100C5F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'water pipe'!$A$1:$K$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'water pipe'!$A$1:$K$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -117,24 +117,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Length (m)</t>
   </si>
   <si>
@@ -157,9 +142,6 @@
   </si>
   <si>
     <t>Location:- Shankharapur Municipality 1</t>
-  </si>
-  <si>
-    <t>-13% VAT for material</t>
   </si>
   <si>
     <t>-for pipe laying</t>
@@ -396,7 +378,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -500,6 +482,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -521,21 +509,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1063,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
@@ -1091,113 +1064,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
     </row>
     <row r="2" spans="1:25" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:25" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="A6" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="H6" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -1249,10 +1222,10 @@
     </row>
     <row r="9" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7"/>
@@ -1269,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1297,7 +1270,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C11" s="19">
         <v>1</v>
@@ -1323,7 +1296,7 @@
     <row r="12" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="1"/>
@@ -1334,14 +1307,15 @@
         <v>16.875</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I12" s="2">
-        <v>748.9</v>
+        <f>1.15*748.9</f>
+        <v>861.2349999999999</v>
       </c>
       <c r="J12" s="38">
         <f>G12*I12</f>
-        <v>12637.6875</v>
+        <v>14533.340624999999</v>
       </c>
       <c r="K12" s="14"/>
       <c r="M12" s="9"/>
@@ -1376,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -1404,7 +1378,7 @@
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C15" s="19">
         <f>C11</f>
@@ -1428,7 +1402,7 @@
     <row r="16" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="1"/>
@@ -1439,15 +1413,15 @@
         <v>250</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I16" s="2">
-        <f>6461.51/1000</f>
-        <v>6.4615100000000005</v>
+        <f>1.15*6461.51/1000</f>
+        <v>7.4307365000000001</v>
       </c>
       <c r="J16" s="38">
         <f>G16*I16</f>
-        <v>1615.3775000000001</v>
+        <v>1857.684125</v>
       </c>
       <c r="K16" s="14"/>
       <c r="M16" s="9"/>
@@ -1495,17 +1469,17 @@
         <v>3</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>32</v>
       </c>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
@@ -1516,7 +1490,7 @@
     <row r="19" spans="1:25" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="40" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C19" s="22">
         <f>C15</f>
@@ -1569,7 +1543,7 @@
         <v>202</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I20" s="2">
         <v>287</v>
@@ -1582,9 +1556,7 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
-      <c r="B21" s="18" t="s">
-        <v>35</v>
-      </c>
+      <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
@@ -1592,203 +1564,115 @@
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
-      <c r="J21" s="16">
-        <f>0.13*J20</f>
-        <v>7536.62</v>
-      </c>
+      <c r="J21" s="19"/>
       <c r="K21" s="19"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-    </row>
-    <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+    <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
         <v>4</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C22" s="13">
         <v>1</v>
       </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="15">
+        <f t="shared" ref="G22" si="2">PRODUCT(C22:F22)</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="2">
+        <v>500</v>
+      </c>
+      <c r="J22" s="15">
+        <f>G22*I22</f>
+        <v>500</v>
+      </c>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="1"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="15">
-        <f t="shared" ref="G23" si="2">PRODUCT(C23:F23)</f>
-        <v>1</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="2">
-        <v>500</v>
-      </c>
-      <c r="J23" s="15">
-        <f>G23*I23</f>
-        <v>500</v>
-      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="16"/>
       <c r="K23" s="14"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="14"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26" t="s">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16">
-        <f>SUM(J9:J23)</f>
-        <v>80263.684999999998</v>
-      </c>
-      <c r="K25" s="29"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-    </row>
-    <row r="27" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="22" t="s">
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16">
+        <f>SUM(J9:J22)</f>
+        <v>74865.024749999997</v>
+      </c>
+      <c r="K24" s="29"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+    </row>
+    <row r="26" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="49">
-        <f>J25</f>
-        <v>80263.684999999998</v>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="31">
-        <v>100</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="35"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B28" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="51">
-        <v>70000</v>
-      </c>
-      <c r="D28" s="52"/>
-      <c r="E28" s="31"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B29" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="51">
-        <f>C28-C31-C32</f>
-        <v>66500</v>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="31">
-        <f>C29/C27*100</f>
-        <v>82.851914910211264</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="53">
-        <f>C27-C29</f>
-        <v>13763.684999999998</v>
-      </c>
-      <c r="D30" s="53"/>
-      <c r="E30" s="31">
-        <f>100-E29</f>
-        <v>17.148085089788736</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="49">
-        <f>C28*0.03</f>
-        <v>2100</v>
-      </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="49">
-        <f>C28*0.02</f>
-        <v>1400</v>
-      </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="31">
-        <v>2</v>
-      </c>
+      <c r="C26" s="41">
+        <f>J24</f>
+        <v>74865.024749999997</v>
+      </c>
+      <c r="D26" s="42"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="35"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
+  <mergeCells count="10">
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -1798,6 +1682,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
